--- a/www/flightdata/xlsx/eoss-337.xlsx
+++ b/www/flightdata/xlsx/eoss-337.xlsx
@@ -2793,7 +2793,7 @@
         <v>19250.56</v>
       </c>
       <c r="I2">
-        <v>454</v>
+        <v>329</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
